--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F72496B-EB95-40AF-BC4A-B143DC04F2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BC2B7-F14E-46C2-96A1-A5D4D62A0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="88">
   <si>
     <t>TC ID</t>
   </si>
@@ -107,18 +107,9 @@
     <t>Reimbursement Claim</t>
   </si>
   <si>
-    <t>Fuel</t>
-  </si>
-  <si>
-    <t>C:\Automation\Test cases Novated App\Filestoupload\Invoice.pdf</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>22 Apr 2026</t>
-  </si>
-  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -140,13 +131,172 @@
     <t>${TC001.Odometer}</t>
   </si>
   <si>
-    <t>5016</t>
-  </si>
-  <si>
-    <t>REQ-621</t>
-  </si>
-  <si>
     <t>Maintenance</t>
+  </si>
+  <si>
+    <t>C:\Users\Public\Documents\Invoice.pdf</t>
+  </si>
+  <si>
+    <t>Tax Invoice</t>
+  </si>
+  <si>
+    <t>12301</t>
+  </si>
+  <si>
+    <t>4 May 2026</t>
+  </si>
+  <si>
+    <t>REQ-652</t>
+  </si>
+  <si>
+    <t>End Of Lease Date</t>
+  </si>
+  <si>
+    <t>30/08/2029 10:00 GMT+10:00</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
+    <t>Toshihiko Inafune</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Unassigned</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>TC006</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
+    <t>TC008</t>
+  </si>
+  <si>
+    <t>${TC003.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC003.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC003.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC003.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>Tyres</t>
+  </si>
+  <si>
+    <t>Vehicle General maintenance has been completed</t>
+  </si>
+  <si>
+    <t>12303</t>
+  </si>
+  <si>
+    <t>REQ-622</t>
+  </si>
+  <si>
+    <t>11/02/2026 11:00 GMT+11:00</t>
+  </si>
+  <si>
+    <t>David Cracknell</t>
+  </si>
+  <si>
+    <t>22 Apr 2026 04:33 AM</t>
+  </si>
+  <si>
+    <t>Submitted On</t>
+  </si>
+  <si>
+    <t>22 Apr 2026 04:34 AM</t>
+  </si>
+  <si>
+    <t>Updated On</t>
+  </si>
+  <si>
+    <t>10,063 km</t>
+  </si>
+  <si>
+    <t>$400.00</t>
+  </si>
+  <si>
+    <t>Rotate &amp; Balance Wheels</t>
+  </si>
+  <si>
+    <t>Tyre Puncture</t>
+  </si>
+  <si>
+    <t>12,305 km</t>
+  </si>
+  <si>
+    <t>$200.00</t>
+  </si>
+  <si>
+    <t>5 May 2026</t>
+  </si>
+  <si>
+    <t>12306</t>
+  </si>
+  <si>
+    <t>${TC005.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC007.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC005.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC007.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC005.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC005.Odometer}</t>
+  </si>
+  <si>
+    <t>${TC007.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC007.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC007.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC007.Odometer}</t>
+  </si>
+  <si>
+    <t>REQ-660</t>
+  </si>
+  <si>
+    <t>12308</t>
+  </si>
+  <si>
+    <t>7 May 2026</t>
   </si>
 </sst>
 </file>
@@ -154,14 +304,35 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,6 +355,12 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -227,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -235,7 +412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -244,11 +421,32 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -547,29 +745,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="10" width="23.77734375" customWidth="1"/>
-    <col min="11" max="11" width="17.21875" customWidth="1"/>
-    <col min="12" max="12" width="19.88671875" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="19.33203125" customWidth="1"/>
-    <col min="17" max="17" width="18.44140625" customWidth="1"/>
-    <col min="18" max="23" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.5546875"/>
+    <col min="2" max="2" customWidth="true" width="20.6640625"/>
+    <col min="3" max="4" customWidth="true" width="24.33203125"/>
+    <col min="5" max="5" customWidth="true" width="27.33203125"/>
+    <col min="6" max="6" customWidth="true" width="16.77734375"/>
+    <col min="7" max="7" customWidth="true" width="15.33203125"/>
+    <col min="8" max="8" customWidth="true" width="21.77734375"/>
+    <col min="9" max="9" customWidth="true" width="18.6640625"/>
+    <col min="10" max="10" customWidth="true" width="23.77734375"/>
+    <col min="11" max="11" customWidth="true" width="17.21875"/>
+    <col min="12" max="12" customWidth="true" width="19.88671875"/>
+    <col min="13" max="13" customWidth="true" width="20.6640625"/>
+    <col min="14" max="14" customWidth="true" width="17.5546875"/>
+    <col min="15" max="15" customWidth="true" width="14.6640625"/>
+    <col min="16" max="16" customWidth="true" width="19.33203125"/>
+    <col min="17" max="17" customWidth="true" width="18.44140625"/>
+    <col min="18" max="22" customWidth="true" width="19.109375"/>
+    <col min="23" max="23" customWidth="true" width="25.6640625"/>
+    <col min="24" max="24" customWidth="true" style="9" width="27.109375"/>
+    <col min="25" max="25" customWidth="true" width="25.33203125"/>
+    <col min="26" max="26" customWidth="true" width="19.5546875"/>
+    <col min="27" max="27" customWidth="true" width="14.5546875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="9" width="17.21875"/>
+    <col min="29" max="29" customWidth="true" style="9" width="15.109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -636,9 +841,30 @@
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3"/>
+      <c r="W1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD1" s="14"/>
     </row>
-    <row r="2" spans="1:23" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -646,144 +872,662 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="D2" s="5">
         <f>C2+1</f>
         <v>5017</v>
       </c>
       <c r="E2" s="5">
-        <f>D2+1</f>
-        <v>5018</v>
-      </c>
-      <c r="F2" s="9" t="s">
+        <f>C2+1</f>
+        <v>12302</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="11">
+        <v>600</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="4">
-        <v>300</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="V2" s="6" t="str">
+        <f>TEXT(E2,"#,##0")&amp;" km"</f>
+        <v>12,302 km</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+    </row>
+    <row r="3" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" s="7" t="str">
-        <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>5,018 km</v>
-      </c>
-      <c r="W2" s="7"/>
-    </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="11">
+        <v>600</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="4">
-        <v>300</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" s="4" t="s">
+      <c r="W3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="V3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" s="4"/>
+      <c r="X3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="E5" s="6"/>
+    <row r="4" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="5">
+        <f>C4+1</f>
+        <v>12302</v>
+      </c>
+      <c r="E4" s="5">
+        <f>C4+1</f>
+        <v>12304</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="11">
+        <v>500</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="6" t="str">
+        <f>TEXT(E4,"#,##0")&amp;" km"</f>
+        <v>12,304 km</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="U10" s="8"/>
+    <row r="5" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="5">
+        <f>C6+1</f>
+        <v>12302</v>
+      </c>
+      <c r="E6" s="5">
+        <f>C6+1</f>
+        <v>12302</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V6" s="6" t="str">
+        <f>TEXT(E6,"#,##0")&amp;" km"</f>
+        <v>12,302 km</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+    </row>
+    <row r="7" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="11">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+    </row>
+    <row r="8" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="5">
+        <f>C8+1</f>
+        <v>12302</v>
+      </c>
+      <c r="E8" s="5">
+        <f>C8+1</f>
+        <v>12307</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+    </row>
+    <row r="9" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="U10" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0BC2B7-F14E-46C2-96A1-A5D4D62A0D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C8D21A-4CF6-4ACF-BCF1-47F55930EEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="122">
   <si>
     <t>TC ID</t>
   </si>
@@ -140,15 +140,6 @@
     <t>Tax Invoice</t>
   </si>
   <si>
-    <t>12301</t>
-  </si>
-  <si>
-    <t>4 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-652</t>
-  </si>
-  <si>
     <t>End Of Lease Date</t>
   </si>
   <si>
@@ -206,18 +197,6 @@
     <t>Vehicle General maintenance has been completed</t>
   </si>
   <si>
-    <t>12303</t>
-  </si>
-  <si>
-    <t>REQ-622</t>
-  </si>
-  <si>
-    <t>11/02/2026 11:00 GMT+11:00</t>
-  </si>
-  <si>
-    <t>David Cracknell</t>
-  </si>
-  <si>
     <t>22 Apr 2026 04:33 AM</t>
   </si>
   <si>
@@ -230,82 +209,196 @@
     <t>Updated On</t>
   </si>
   <si>
-    <t>10,063 km</t>
-  </si>
-  <si>
-    <t>$400.00</t>
-  </si>
-  <si>
     <t>Rotate &amp; Balance Wheels</t>
   </si>
   <si>
     <t>Tyre Puncture</t>
   </si>
   <si>
-    <t>12,305 km</t>
+    <t>${TC005.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC007.Last Odometer Reading}</t>
+  </si>
+  <si>
+    <t>${TC005.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC007.New Odometer}</t>
+  </si>
+  <si>
+    <t>${TC005.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC005.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC005.Odometer}</t>
+  </si>
+  <si>
+    <t>${TC007.Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC007.Last Reading Date}</t>
+  </si>
+  <si>
+    <t>${TC007.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC007.Odometer}</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Toshihiko</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Inafune</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>inafune@jfcaust.com.au.test</t>
+  </si>
+  <si>
+    <t>Primary Email</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Test Employer</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Vehicle Description</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
+  </si>
+  <si>
+    <t>FTV21M</t>
+  </si>
+  <si>
+    <t>Registration Number</t>
+  </si>
+  <si>
+    <t>Registration State</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Auto Lease</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Status1</t>
+  </si>
+  <si>
+    <t>Updated By1</t>
+  </si>
+  <si>
+    <t>Assigned To1</t>
+  </si>
+  <si>
+    <t>${TC003.Reference Number}</t>
+  </si>
+  <si>
+    <t>${TC003.Odometer}</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>12360</t>
+  </si>
+  <si>
+    <t>22 May 2026</t>
+  </si>
+  <si>
+    <t>REQ-810</t>
+  </si>
+  <si>
+    <t>12361</t>
+  </si>
+  <si>
+    <t>REQ-811</t>
+  </si>
+  <si>
+    <t>12362</t>
+  </si>
+  <si>
+    <t>REQ-812</t>
+  </si>
+  <si>
+    <t>12363</t>
+  </si>
+  <si>
+    <t>REQ-813</t>
+  </si>
+  <si>
+    <t>$600.00</t>
+  </si>
+  <si>
+    <t>$500.00</t>
+  </si>
+  <si>
+    <t>$1,000.00</t>
   </si>
   <si>
     <t>$200.00</t>
   </si>
   <si>
-    <t>5 May 2026</t>
-  </si>
-  <si>
-    <t>12306</t>
-  </si>
-  <si>
-    <t>${TC005.Last Odometer Reading}</t>
-  </si>
-  <si>
-    <t>${TC007.Last Odometer Reading}</t>
-  </si>
-  <si>
-    <t>${TC005.New Odometer}</t>
-  </si>
-  <si>
-    <t>${TC007.New Odometer}</t>
-  </si>
-  <si>
-    <t>${TC005.Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC005.Last Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC005.Reference Number}</t>
-  </si>
-  <si>
-    <t>${TC005.Odometer}</t>
-  </si>
-  <si>
-    <t>${TC007.Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC007.Last Reading Date}</t>
-  </si>
-  <si>
-    <t>${TC007.Reference Number}</t>
-  </si>
-  <si>
-    <t>${TC007.Odometer}</t>
-  </si>
-  <si>
-    <t>REQ-660</t>
-  </si>
-  <si>
-    <t>12308</t>
-  </si>
-  <si>
-    <t>7 May 2026</t>
-  </si>
-  <si>
-    <t>12322</t>
-  </si>
-  <si>
-    <t>20 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-744</t>
+    <t>12374</t>
+  </si>
+  <si>
+    <t>23 May 2026</t>
+  </si>
+  <si>
+    <t>REQ-825</t>
+  </si>
+  <si>
+    <t>12375</t>
+  </si>
+  <si>
+    <t>REQ-826</t>
+  </si>
+  <si>
+    <t>12376</t>
+  </si>
+  <si>
+    <t>REQ-827</t>
+  </si>
+  <si>
+    <t>12377</t>
+  </si>
+  <si>
+    <t>REQ-828</t>
   </si>
 </sst>
 </file>
@@ -321,13 +414,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -371,6 +457,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1E1B13"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -413,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -421,7 +513,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -433,32 +525,27 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,36 +841,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD10"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AS10"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.5546875"/>
-    <col min="2" max="2" customWidth="true" width="20.6640625"/>
-    <col min="3" max="4" customWidth="true" width="24.33203125"/>
-    <col min="5" max="5" customWidth="true" width="27.33203125"/>
-    <col min="6" max="6" customWidth="true" width="16.77734375"/>
-    <col min="7" max="7" customWidth="true" width="15.33203125"/>
-    <col min="8" max="8" customWidth="true" width="21.77734375"/>
-    <col min="9" max="9" customWidth="true" width="18.6640625"/>
-    <col min="10" max="10" customWidth="true" width="23.77734375"/>
-    <col min="11" max="11" customWidth="true" width="17.21875"/>
-    <col min="12" max="12" customWidth="true" width="19.88671875"/>
-    <col min="13" max="13" customWidth="true" width="20.6640625"/>
-    <col min="14" max="14" customWidth="true" width="17.5546875"/>
-    <col min="15" max="15" customWidth="true" width="14.6640625"/>
-    <col min="16" max="16" customWidth="true" width="19.33203125"/>
-    <col min="17" max="17" customWidth="true" width="18.44140625"/>
-    <col min="18" max="22" customWidth="true" width="19.109375"/>
-    <col min="23" max="23" customWidth="true" width="25.6640625"/>
-    <col min="24" max="24" customWidth="true" style="9" width="27.109375"/>
-    <col min="25" max="25" customWidth="true" width="25.33203125"/>
-    <col min="26" max="26" customWidth="true" width="19.5546875"/>
-    <col min="27" max="27" customWidth="true" width="14.5546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="9" width="17.21875"/>
-    <col min="29" max="29" customWidth="true" style="9" width="15.109375"/>
+    <col min="1" max="1" customWidth="true" width="8.5"/>
+    <col min="2" max="2" customWidth="true" width="20.625"/>
+    <col min="3" max="4" customWidth="true" width="24.375"/>
+    <col min="5" max="5" customWidth="true" width="27.375"/>
+    <col min="6" max="6" customWidth="true" width="16.75"/>
+    <col min="7" max="7" customWidth="true" width="15.375"/>
+    <col min="8" max="8" customWidth="true" width="21.75"/>
+    <col min="9" max="9" customWidth="true" width="18.625"/>
+    <col min="10" max="10" customWidth="true" width="23.75"/>
+    <col min="11" max="11" customWidth="true" width="17.25"/>
+    <col min="12" max="12" customWidth="true" width="19.875"/>
+    <col min="13" max="13" customWidth="true" width="20.625"/>
+    <col min="14" max="14" customWidth="true" width="17.5"/>
+    <col min="15" max="15" customWidth="true" width="14.625"/>
+    <col min="16" max="16" customWidth="true" width="19.375"/>
+    <col min="17" max="17" customWidth="true" width="18.5"/>
+    <col min="18" max="22" customWidth="true" width="19.125"/>
+    <col min="23" max="23" customWidth="true" width="25.625"/>
+    <col min="24" max="24" customWidth="true" style="9" width="27.125"/>
+    <col min="25" max="25" customWidth="true" width="25.375"/>
+    <col min="26" max="26" customWidth="true" width="19.5"/>
+    <col min="27" max="27" customWidth="true" width="14.5"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="9" width="17.25"/>
+    <col min="29" max="29" customWidth="true" style="9" width="15.125"/>
+    <col min="31" max="31" customWidth="true" width="11.125"/>
+    <col min="32" max="32" customWidth="true" width="11.875"/>
+    <col min="33" max="33" customWidth="true" width="27.875"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="9" width="9.875"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="20.125"/>
+    <col min="40" max="42" customWidth="true" width="12.875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -854,26 +947,73 @@
         <v>34</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Y1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="AB1" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD1" s="14"/>
+        <v>57</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH1" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL1" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN1" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO1" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS1" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -881,21 +1021,21 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="D2" s="5" t="n">
         <f>C2+1</f>
-        <v>12309.0</v>
+        <v>12375.0</v>
       </c>
       <c r="E2" s="5" t="n">
         <f>C2+1</f>
-        <v>12309.0</v>
+        <v>12375.0</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="11">
-        <v>600</v>
+      <c r="G2" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>33</v>
@@ -904,7 +1044,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
@@ -931,17 +1071,17 @@
         <v>24</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="V2" s="6" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,309 km</v>
+        <v>12,375 km</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>33</v>
@@ -952,8 +1092,24 @@
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="4"/>
+      <c r="AJ2" s="14"/>
+      <c r="AK2" s="4"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="4"/>
+      <c r="AQ2" s="4"/>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="14"/>
     </row>
-    <row r="3" spans="1:30" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -970,8 +1126,8 @@
       <c r="F3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="11">
-        <v>600</v>
+      <c r="G3" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>33</v>
@@ -980,7 +1136,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
@@ -1022,43 +1178,91 @@
         <v>33</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Y3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
+      <c r="AD3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH3" s="14">
+        <v>469750861</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ3" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ3" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS3" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D4" s="5" t="n">
         <f>C4+1</f>
-        <v>12304.0</v>
+        <v>12376.0</v>
       </c>
       <c r="E4" s="5" t="n">
         <f>C4+1</f>
-        <v>12304.0</v>
+        <v>12376.0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="11">
-        <v>500</v>
+        <v>52</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>33</v>
@@ -1094,17 +1298,17 @@
         <v>24</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="V4" s="6" t="str">
         <f>TEXT(E4,"#,##0")&amp;" km"</f>
-        <v>12,304 km</v>
+        <v>12,376 km</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1115,26 +1319,42 @@
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="4"/>
+      <c r="AG4" s="4"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="4"/>
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="4"/>
+      <c r="AL4" s="14"/>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="14"/>
+      <c r="AO4" s="14"/>
+      <c r="AP4" s="4"/>
+      <c r="AQ4" s="4"/>
+      <c r="AR4" s="14"/>
+      <c r="AS4" s="14"/>
     </row>
-    <row r="5" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>66</v>
+      <c r="G5" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>33</v>
@@ -1170,62 +1390,110 @@
         <v>24</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="V5" s="13" t="s">
-        <v>65</v>
+        <v>97</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>60</v>
+        <v>38</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="AA5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH5" s="14">
+        <v>469750861</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL5" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO5" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="AP5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS5" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="D6" s="5" t="n">
         <f>C6+1</f>
-        <v>12302.0</v>
+        <v>12377.0</v>
       </c>
       <c r="E6" s="5" t="n">
         <f>C6+1</f>
-        <v>12302.0</v>
+        <v>12377.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1000</v>
+        <v>58</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>33</v>
@@ -1261,17 +1529,17 @@
         <v>24</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="V6" s="6" t="str">
         <f>TEXT(E6,"#,##0")&amp;" km"</f>
-        <v>12,302 km</v>
+        <v>12,377 km</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>33</v>
@@ -1282,26 +1550,42 @@
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="4"/>
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
     </row>
-    <row r="7" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="11">
-        <v>1000</v>
+        <v>58</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>33</v>
@@ -1337,58 +1621,106 @@
         <v>24</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Y7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA7" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
+      <c r="AD7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH7" s="14">
+        <v>469750861</v>
+      </c>
+      <c r="AI7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ7" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN7" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS7" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="D8" s="5" t="n">
         <f>C8+1</f>
-        <v>12323.0</v>
+        <v>12378.0</v>
       </c>
       <c r="E8" s="5" t="n">
         <f>C8+1</f>
-        <v>12323.0</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="4">
-        <v>200</v>
+        <v>12378.0</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>33</v>
@@ -1424,50 +1756,67 @@
         <v>24</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>69</v>
+        <v>121</v>
+      </c>
+      <c r="V8" s="6" t="str">
+        <f>TEXT(E8,"#,##0")&amp;" km"</f>
+        <v>12,378 km</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="14"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="14"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="14"/>
+      <c r="AO8" s="14"/>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="14"/>
+      <c r="AS8" s="14"/>
     </row>
-    <row r="9" spans="1:30" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>33</v>
@@ -1503,40 +1852,88 @@
         <v>24</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="W9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA9" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="Z9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
+      <c r="AD9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH9" s="14">
+        <v>469750861</v>
+      </c>
+      <c r="AI9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL9" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS9" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" ht="14.25" x14ac:dyDescent="0.2">
       <c r="U10" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/NovatedApp_Regression/01_NovatedApp_Regression.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhana\IdeaProjects\NovatedApp\cucumber-for-appian\src\test\resources\testdata\NovatedApp_Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C8D21A-4CF6-4ACF-BCF1-47F55930EEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9BC59-F562-4110-9709-98F2C8EB267B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="138">
   <si>
     <t>TC ID</t>
   </si>
@@ -143,9 +143,6 @@
     <t>End Of Lease Date</t>
   </si>
   <si>
-    <t>30/08/2029 10:00 GMT+10:00</t>
-  </si>
-  <si>
     <t>Submitted By</t>
   </si>
   <si>
@@ -335,33 +332,6 @@
     <t>Cancelled</t>
   </si>
   <si>
-    <t>12360</t>
-  </si>
-  <si>
-    <t>22 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-810</t>
-  </si>
-  <si>
-    <t>12361</t>
-  </si>
-  <si>
-    <t>REQ-811</t>
-  </si>
-  <si>
-    <t>12362</t>
-  </si>
-  <si>
-    <t>REQ-812</t>
-  </si>
-  <si>
-    <t>12363</t>
-  </si>
-  <si>
-    <t>REQ-813</t>
-  </si>
-  <si>
     <t>$600.00</t>
   </si>
   <si>
@@ -374,31 +344,109 @@
     <t>$200.00</t>
   </si>
   <si>
-    <t>12374</t>
-  </si>
-  <si>
-    <t>23 May 2026</t>
-  </si>
-  <si>
-    <t>REQ-825</t>
-  </si>
-  <si>
-    <t>12375</t>
-  </si>
-  <si>
-    <t>REQ-826</t>
-  </si>
-  <si>
-    <t>12376</t>
-  </si>
-  <si>
-    <t>REQ-827</t>
-  </si>
-  <si>
-    <t>12377</t>
-  </si>
-  <si>
-    <t>REQ-828</t>
+    <t>1 Jun 2026</t>
+  </si>
+  <si>
+    <t>5539</t>
+  </si>
+  <si>
+    <t>REQ-891</t>
+  </si>
+  <si>
+    <t>5540</t>
+  </si>
+  <si>
+    <t>REQ-892</t>
+  </si>
+  <si>
+    <t>5541</t>
+  </si>
+  <si>
+    <t>REQ-893</t>
+  </si>
+  <si>
+    <t>5555</t>
+  </si>
+  <si>
+    <t>REQ-914</t>
+  </si>
+  <si>
+    <t>${TC001.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC003.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC005.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>${TC007.End Of Lease Date}</t>
+  </si>
+  <si>
+    <t>30 Aug 2029</t>
+  </si>
+  <si>
+    <t>5556</t>
+  </si>
+  <si>
+    <t>2 Jun 2026</t>
+  </si>
+  <si>
+    <t>REQ-920</t>
+  </si>
+  <si>
+    <t>5557</t>
+  </si>
+  <si>
+    <t>REQ-921</t>
+  </si>
+  <si>
+    <t>5558</t>
+  </si>
+  <si>
+    <t>REQ-922</t>
+  </si>
+  <si>
+    <t>5559</t>
+  </si>
+  <si>
+    <t>REQ-923</t>
+  </si>
+  <si>
+    <t>5560</t>
+  </si>
+  <si>
+    <t>REQ-924</t>
+  </si>
+  <si>
+    <t>5561</t>
+  </si>
+  <si>
+    <t>REQ-926</t>
+  </si>
+  <si>
+    <t>5562</t>
+  </si>
+  <si>
+    <t>REQ-927</t>
+  </si>
+  <si>
+    <t>5563</t>
+  </si>
+  <si>
+    <t>REQ-928</t>
+  </si>
+  <si>
+    <t>5564</t>
+  </si>
+  <si>
+    <t>REQ-929</t>
+  </si>
+  <si>
+    <t>5565</t>
+  </si>
+  <si>
+    <t>REQ-930</t>
   </si>
 </sst>
 </file>
@@ -841,7 +889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="8.5"/>
@@ -873,10 +921,10 @@
     <col min="33" max="33" customWidth="true" width="27.875"/>
     <col min="34" max="34" bestFit="true" customWidth="true" style="9" width="9.875"/>
     <col min="37" max="37" bestFit="true" customWidth="true" width="20.125"/>
-    <col min="40" max="42" customWidth="true" width="12.875"/>
+    <col min="40" max="41" customWidth="true" width="12.875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:44" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -950,70 +998,67 @@
         <v>35</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AA1" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="AB1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AH1" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="AI1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AJ1" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="AK1" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="AL1" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AM1" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="AN1" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AO1" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AR1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS1" s="13" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="2" spans="1:45" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:44" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>22</v>
       </c>
@@ -1021,21 +1066,21 @@
         <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="D2" s="5" t="n">
         <f>C2+1</f>
-        <v>12375.0</v>
+        <v>5563.0</v>
       </c>
       <c r="E2" s="5" t="n">
         <f>C2+1</f>
-        <v>12375.0</v>
+        <v>5563.0</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>33</v>
@@ -1044,7 +1089,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>24</v>
@@ -1071,24 +1116,30 @@
         <v>24</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="V2" s="6" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>12,375 km</v>
+        <v>5,563 km</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
+      <c r="X2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
@@ -1104,12 +1155,17 @@
       <c r="AM2" s="4"/>
       <c r="AN2" s="14"/>
       <c r="AO2" s="14"/>
-      <c r="AP2" s="4"/>
-      <c r="AQ2" s="4"/>
-      <c r="AR2" s="14"/>
-      <c r="AS2" s="14"/>
+      <c r="AP2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR2" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="3" spans="1:45" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:44" s="2" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>25</v>
       </c>
@@ -1127,7 +1183,7 @@
         <v>32</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>33</v>
@@ -1136,7 +1192,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
@@ -1178,91 +1234,88 @@
         <v>33</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AE3" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="AF3" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH3" s="14">
         <v>469750861</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ3" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL3" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AL3" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN3" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP3" s="4" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="AP3" s="14" t="s">
+        <v>91</v>
       </c>
       <c r="AQ3" s="14" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="AR3" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="AS3" s="14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="D4" s="5" t="n">
         <f>C4+1</f>
-        <v>12376.0</v>
+        <v>5564.0</v>
       </c>
       <c r="E4" s="5" t="n">
         <f>C4+1</f>
-        <v>12376.0</v>
+        <v>5564.0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>33</v>
@@ -1298,24 +1351,30 @@
         <v>24</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="V4" s="6" t="str">
         <f>TEXT(E4,"#,##0")&amp;" km"</f>
-        <v>12,376 km</v>
+        <v>5,564 km</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
+      <c r="X4" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -1331,30 +1390,35 @@
       <c r="AM4" s="4"/>
       <c r="AN4" s="14"/>
       <c r="AO4" s="14"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="14"/>
-      <c r="AS4" s="14"/>
+      <c r="AP4" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR4" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="5" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>33</v>
@@ -1390,110 +1454,107 @@
         <v>24</v>
       </c>
       <c r="S5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="T5" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="U5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="V5" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AD5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AE5" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="AF5" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH5" s="14">
         <v>469750861</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ5" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL5" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AL5" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM5" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN5" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="AP5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AQ5" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="AP5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ5" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="AR5" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS5" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D6" s="5" t="n">
         <f>C6+1</f>
-        <v>12377.0</v>
+        <v>5565.0</v>
       </c>
       <c r="E6" s="5" t="n">
         <f>C6+1</f>
-        <v>12377.0</v>
+        <v>5565.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>33</v>
@@ -1529,24 +1590,30 @@
         <v>24</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="V6" s="6" t="str">
         <f>TEXT(E6,"#,##0")&amp;" km"</f>
-        <v>12,377 km</v>
+        <v>5,565 km</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
+      <c r="X6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1562,30 +1629,35 @@
       <c r="AM6" s="4"/>
       <c r="AN6" s="14"/>
       <c r="AO6" s="14"/>
-      <c r="AP6" s="4"/>
-      <c r="AQ6" s="4"/>
-      <c r="AR6" s="14"/>
-      <c r="AS6" s="14"/>
+      <c r="AP6" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR6" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="7" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>33</v>
@@ -1621,106 +1693,103 @@
         <v>24</v>
       </c>
       <c r="S7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AE7" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="AF7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH7" s="14">
         <v>469750861</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ7" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL7" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AL7" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM7" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN7" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AO7" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="AP7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AQ7" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
+      </c>
+      <c r="AP7" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="AR7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS7" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D8" s="5" t="n">
         <f>C8+1</f>
-        <v>12378.0</v>
+        <v>5566.0</v>
       </c>
       <c r="E8" s="5" t="n">
         <f>C8+1</f>
-        <v>12378.0</v>
+        <v>5566.0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>33</v>
@@ -1756,27 +1825,29 @@
         <v>24</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="U8" s="4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="V8" s="6" t="str">
         <f>TEXT(E8,"#,##0")&amp;" km"</f>
-        <v>12,378 km</v>
+        <v>5,566 km</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="X8" s="4"/>
+      <c r="X8" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="Y8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -1793,30 +1864,35 @@
       <c r="AM8" s="4"/>
       <c r="AN8" s="14"/>
       <c r="AO8" s="14"/>
-      <c r="AP8" s="4"/>
-      <c r="AQ8" s="4"/>
-      <c r="AR8" s="14"/>
-      <c r="AS8" s="14"/>
+      <c r="AP8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR8" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="9" spans="1:45" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:44" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>33</v>
@@ -1852,84 +1928,81 @@
         <v>24</v>
       </c>
       <c r="S9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="T9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="U9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="V9" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="W9" s="4" t="s">
         <v>33</v>
       </c>
       <c r="X9" s="4" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="Y9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
       <c r="AD9" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="AE9" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="AF9" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AG9" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AH9" s="14">
         <v>469750861</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AJ9" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AK9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AL9" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AM9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AN9" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AO9" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AP9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AQ9" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="AQ9" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="AR9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="AS9" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:45" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="14.25" x14ac:dyDescent="0.2">
       <c r="U10" s="7"/>
     </row>
   </sheetData>
